--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,4 +814,642 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.006482795447817149</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.004084357836404198</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.00255279528090989</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.002360664236207587</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.00175960271238778</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0008415804511502862</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>40</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.001107204959212314</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000527521560203639</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000356626030612242</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0009606056439906682</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0007242920144866535</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0003587974820122629</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0003170748164007631</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001997751890454228</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.683386152713107e-05</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>75</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0006442666036751823</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001698432009482523</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.026834527534472e-05</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0003265143249860511</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.545586472861118e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.21021916534377e-05</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0003312253452051975</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001348607876460352</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.643824799659806e-05</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0001659557910459304</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001352143743783592</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.806019452744672e-05</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>130</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0003963809779413095</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.770693203636349e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.390484207471783e-05</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>150</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.00214465182140818</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.487293443683856e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.205786123454349e-05</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>200</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01053000416087543</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0002342687957467636</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1903006076753399</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,4 +1453,458 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.05156601935548021</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002713229795155201</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10270.86781657075</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.03677169040476184</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0007815029973790754</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.01904470748931235</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.3929083926750221</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.008175466085361117</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8802907016262673</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.001452144936402809</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000161819021646145</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.039809039881162e-05</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0003202658625562153</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001440461034304764</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.140712978096564e-05</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0003312253452051975</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001348607876460352</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.643824799659806e-05</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0003396740702406441</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001252096533051851</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.120084325762182e-05</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.000348097250706204</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001197666945879444</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.825103181962779e-05</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1907,4 +1908,688 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0002879952803027663</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001274329652054472</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.037649636409428e-05</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0002687642235296532</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001277133149649905</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.009600037158036e-05</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0001916433355280134</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001297184731237328</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.076300367360493e-05</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0002386382842113714</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001311746475609748</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.151653540693992e-05</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0003069945743293768</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.000133796359304923</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.356076704857473e-05</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0003192010474566198</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001343240688081586</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.44030863749701e-05</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0003298363931694775</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001347979442099705</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.58938831449498e-05</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0003312253452051975</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001348607876460352</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.643824799659806e-05</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.000332346488713336</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001349116741448053</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.225162471586241e-05</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0003324872653560226</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001349180742215257</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.00265652689809147</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.0003325999816533934</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001349232000954814</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.006142341711556119</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.000332614078376154</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001349238410363252</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0003271108972311516</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>100</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0003326253595189561</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.000134924354082868</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001792589696759944</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2592,4 +2593,504 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_error_rel</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>l2_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0003098096145459363</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001265560853601585</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.237881523445245e-05</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.000257127371984626</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001276352523941691</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.945338456117915e-05</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>100</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0002072687005916782</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001294016581067297</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.002170469579728e-05</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0002726177933640617</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001318186945647325</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.101675100543284e-05</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0003312253452051975</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001348607876460352</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.643824799659806e-05</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>100</v>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0002646246244008613</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001318537322580875</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001094427864724506</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0001960050666992017</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001294424966442789</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001301109572204202</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0002505699076163258</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001276707805594323</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001060947981882713</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0003098096135561255</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001265560851267838</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.237881511140862e-05</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.463890730886225</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.017595837141983</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.348955088616178</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.00060569843820811</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.961359096988041e-05</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>121.1323765226308</v>
+      </c>
+      <c r="L13" t="n">
+        <v>62.30440780319345</v>
+      </c>
+      <c r="M13" t="n">
+        <v>71.58866890154286</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0024218087495398</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0001587971976347948</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0004159406925375863</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0002792616504726184</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0007986994109056718</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001462010985494495</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0008326388264384957</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.25462632687423e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.26689009747974e-06</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.261398608516743e-05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0002095240703254367</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.514733327199486e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0001071530736146131</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5.465801500191467e-05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0001825014062970675</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.001303875330366493</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0002029726044278121</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0001819885844779045</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0001047831691648818</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0006761720311647092</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.001110317938037389</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0002842793493439999</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.000179997700315182</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0001503683035883293</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.000525344853683593</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.002751554553347695</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0007313159013922803</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.003876887424444474</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.002435097116850251</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.01369423144132381</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.003336570025281037</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.001446676360579754</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.305950475431586e-06</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4.150355032202837e-06</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.655409724293421e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0002373150550217083</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.033012001111894e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.892939871152911e-05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2.689470317964323e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0002560353508244714</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0009120949415867756</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0001471044735044891</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0004262192704364008</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0004489095424683332</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.001254833851785843</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.005224517225191944</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.002086055130328321</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0001178648918874758</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0001133714016037427</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.001534465956582396</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.01102494685772081</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0007991293974190853</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0004900039886193418</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0001559552011220681</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.13134185797495</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.006731185874443</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.03488809307283722</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.987964077855624e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.256606441685072e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001394059917582809</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.01174736552092059</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0009157875682148308</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.899747745835345e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.404634774492995e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.000192749003454072</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008162881173795959</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.211348215625369e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0004073125842427582</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001972678584281614</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0007941668367649316</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002086506386504574</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003083834759330395</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000113357150051797</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.352935124525957e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000841748944590148</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002160768201459135</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000274762721152804</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.5335619315654e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.684176837059947e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002017708719811856</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001108980318670654</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0002964810553267106</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001733807334171611</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.000104174608974769</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0005029868744020052</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001730279808135156</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004242026532594026</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.004403997824840688</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.00165048467085441</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.008852634769038688</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002090259043015373</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005541086991640128</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.000179997700315182</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001503683035883293</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.000525344853683593</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002751554553347695</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007313159013922803</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003644178539550235</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002370285982128732</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0007422780214500461</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002655028012898577</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0009566641882530772</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.000620406305132659</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0003967517116844821</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.00162506444172343</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002789094365480384</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001131290420569973</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0005752077966228452</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002869187372789845</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0009604123022197869</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.003529739495200413</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.00102106982376767</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001215428987723643</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5.74637220499342e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001868116485226763</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0007097552191140652</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5.190584241853781e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001910877538805477</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001496518393982062</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0005265262636245319</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002026110397043881</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0006781761867566037</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001826970101366232</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001537593920433266</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0005338718815460084</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002001131914221679</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0007005311778657528</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001737018378607513</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001470716671951483</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000479562605083311</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002210329743617875</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.000703185386583507</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003246182913866912</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000213243394769043</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001459847540771978</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002212371332556687</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0007042587848173075</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002026266077381211</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.000168761521887577</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0006214838982172026</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002768033287767603</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007304805226770408</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.000179997700315182</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001503683035883293</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.000525344853683593</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002751554553347695</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007313159013922803</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.000176125797777038</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001555842666368721</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.000518800625823141</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002741820667665247</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0007312550032506907</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001894647157534845</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001514092163024288</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0006067493273601909</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0027353829464934</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.000729646825209</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001221388526938538</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001312238175015813</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0003617495068552336</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002473537484692398</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0007269606212038447</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.000126309865352503</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0001353538025369129</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0004275831106644749</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002228442358746937</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0007210072496864078</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001034608460921959</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001265026909301229</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000301529217410601</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001585720257367029</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0007084359467393332</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001268692455161368</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001263055777139792</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0003841940649523025</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001742292689073111</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0007106805457770027</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0002859773515452301</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001992005654805312</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.001366481567083339</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002473527511540315</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007239140064171111</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.000452145249273561</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0002714293762208562</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001928762176631614</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002613594530403308</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007274718164834039</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001652741214887565</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001491780466777874</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0004574563834429461</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002735620164826008</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0007308548297414465</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.000179997700315182</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001503683035883293</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.000525344853683593</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002751554553347695</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007313159013922803</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001892779911424335</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001525031759293558</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0005281184713287504</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00276442840903472</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007316912394180572</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.000186360546980735</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0001535970626667568</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0005487955210859965</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002766039260089777</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0007317386184445804</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001774022061314939</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0001563569937018322</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0005984687696186551</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002767334748442887</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0007317765197992028</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001766641145358738</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0001569709953232175</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0006081203943532304</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002767489571266802</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0007317812673593962</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.000177123276707547</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001575093948761783</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0006163669738844164</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002767624002728503</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0007317850618246452</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0002084312939293342</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001688931729480697</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0008317394925496633</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002751566795949542</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0007313439256672931</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.001259856355412203</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0003585241636919103</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.002083070793485115</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.00200186350395442</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0007126409438518918</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.005874705822481617</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0007123799471532426</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.004021629357998714</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002000236789385955</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0007062671612957428</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.003510865060554146</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0005979290152414032</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.003634164398198098</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002001443199869242</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0007125447822582569</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.000179997700315182</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001503683035883293</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.000525344853683593</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002751554553347695</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0007313159013922803</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001753285501959189</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001614269541760623</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0007911551077203364</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001931608216487746</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007129642421419568</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0008455182210510557</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0002314614382794919</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.002699360476071614</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001623542636382168</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0007066605039336784</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002083382448584969</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001604520102889632</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0009945237579742331</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001931578643967747</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007128967071332363</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0002084387751928873</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0001688954539485036</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0008317853841778142</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002751566811645112</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007313439283427522</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6274CBF9-FD01-48C8-9E6E-1A54C45D5F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,20 @@
     <sheet name="Eigenvalue Ratio" sheetId="4" r:id="rId5"/>
     <sheet name="Eigenvector Angle" sheetId="5" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.801500332346273e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.471269686715342e-06</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.859235802751305e-05</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0002176519949522025</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.212146249371038e-05</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.702771989899655e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.908511450692359e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>7.120456987991917e-05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0008644382340261051</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4.860625834386745e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.080536487767072e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.192445754240355e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001520135688963173</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0003501549347865986</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002615531870464433</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002234275333600765</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002916600648397085</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0006959510843743557</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002206416400660064</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001300245239314644</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.201411739266026e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.46284274591376e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.481478557769625e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0003807606547942558</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.533151330772884e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.957889734205409e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.965688045235651e-06</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4.072287738464477e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0008910722938288455</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6.193183589200983e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.500523891207917e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.661586334776739e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>8.488413275891502e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001704569081476134</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001355369667439013</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.191339691595907e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.696747208324228e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001784629825252932</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.00128373909150642</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0001916246926077503</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.816575339900874e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.204955098267478e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001737592365718226</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002666078238096026</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003894882462592628</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001888555585317641</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002157796820370891</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0004958803259306349</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.003331840203850115</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001091959903451252</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.87462818654187e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.179143052869761e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.004413042448453267</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.09700216988185015</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001577279252891794</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0002097716922047077</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.467656102981087e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01977284208117368</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5361344909749519</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.007480608613668682</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003606071973524249</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0003785294477386504</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01411338362583379</v>
+      </c>
+      <c r="N14" t="n">
+        <v>13.38539938906217</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.170588457872439</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.003875474871682826</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.004092549129886854</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.03993316693925759</v>
+      </c>
+      <c r="N15" t="n">
+        <v>91.1659313989062</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.154157461653891</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.105228962547754</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1129589009822287</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2593143110436012</v>
+      </c>
+      <c r="N16" t="n">
+        <v>149.0466298871836</v>
+      </c>
+      <c r="O16" t="n">
+        <v>3.147144713592068</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1503797165216105</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01988134651402263</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1564186461810159</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0353264624055512</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.002679063460329752</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.735544120959003e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.916946524515842e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0008756421108444342</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002499902842068025</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0002938384702214362</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000109892415524615</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001079816126201649</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0005364341550315788</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001937919464144019</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0004823109667683654</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001921349158651719</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0001859333023324591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001055428697043445</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.003827745022604003</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000950124982410433</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001729252152697591</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0008130993909263211</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005395524441784528</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.00440422750699006</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.001383921126448995</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0005116941122385587</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0004516302847900445</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001816180637178675</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.005229168882628628</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001841525328686112</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.005387415779053105</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.002943482423282575</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.02363863793300028</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.005828801896084786</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.002441849550257828</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003833515989412616</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002028406338670448</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.002401176036895345</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.003011353782623843</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002189336911124866</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.470671401727519e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.368048055471549e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>8.628005057722873e-05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0004927606130806198</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.094946876200062e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.221801876208574e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.698954392796996e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0001414289540917193</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0006004160828205123</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.839302575592896e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0005842692689906891</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002168095749010168</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0008394463082499839</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0007526850609425173</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0001186386588155291</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.783670036309863e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.586971396614641e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001808697704386091</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0006997182852845101</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.000140690776592499</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001403326025409823</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.376048206840811e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0002532604054110934</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001092385878529567</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0002294217265207654</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0001569531167516791</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0001078320300925344</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.0003334650607214464</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.001490453411118281</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.000368406562248487</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.206015590208944e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6.140365789242741e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001400736115802165</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001313314452206198</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0003206762819213677</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.20239041059689e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.137420681375243e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001397601013390209</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001299342399634782</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.000320259751893624</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.202043885599304e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.136484919528626e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001397805963349067</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001289926441145364</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003198574074045848</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.200580703024203e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.134119968829275e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001397291383426881</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001285343464311731</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000319633641012419</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.204738650410599e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.137764883275358e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001398723982913693</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001283330355368063</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003196400903620746</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.129085571138225e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.379640440944469e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002088730321653659</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002730498043917426</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003896827867413391</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.936499044589814e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.332645641616055e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0001892717225825037</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002729154816989841</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0003897873250535933</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.816575339900874e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.204955098267478e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001737592365718226</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002666078238096026</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003894882462592628</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001112377490791183</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.558540999577595e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0006147155470058725</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002923980913808559</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003912301819288623</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001064451155068369</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.174765102019672e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0002732522082737997</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.00292179536137478</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0003910609333148661</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.723324428368424e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5.387594610132896e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002215230477857555</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002605028068676967</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0003705271387349777</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.155616636314362e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.114336107960329e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.000214640286523451</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002477813267432794</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0003534746830782525</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.943485193830253e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.216965582764522e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001400373598022566</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002259305637807074</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003165184743697351</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.326040776742034e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5.232767904439303e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002642490481271375</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002150052878050701</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0003253068289853818</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.579567807558528e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5.665737790382701e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.001106970189339942</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002387362390002307</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003678009280142716</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001151206895981804</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.55582340464134e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001829021884942287</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002527767998615284</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003783683834472804</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.240683343776807e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5.74552201315785e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002045226293379656</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002650101732551946</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0003881698638801413</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.816575339900874e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.204955098267478e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001737592365718226</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002666078238096026</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003894882462592628</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001948941435250262</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.45142357661005e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001068534620723285</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00267897421459194</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003905587765896297</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001234719119468375</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.62253702772128e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0006524774352321793</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002680593371629891</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0003906937188268117</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0001151987707179724</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6.978557205071808e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0004764016390442441</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.002681890012738286</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0003908015971537191</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0001158643419524319</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.937147187615924e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0004615643457798897</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.002682052242458657</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0003908150940019505</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0001167406230686563</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6.910118054082838e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0004505744430004747</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.002682181923354431</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0003908259702486874</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.854323323279841e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.136565798522225e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0003690094338957035</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.002925499203831176</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0003908400610899826</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.530321740665477e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>6.152563392051647e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001504580766766327</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.002536269206033555</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0003398262122389401</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.086501327490222e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>6.509588556480375e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000111876633230169</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002366552318820776</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.000320513666027455</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.311047666717304e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.047688514311022e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001383531889474987</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.00256537891053648</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.000339350181254865</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.816575339900874e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.204955098267478e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001737592365718226</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.002666078238096026</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003894882462592628</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.513009090213349e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>6.070246534760215e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002940812257959751</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002004178975590628</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003342539533250058</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.069693536281394e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6.831142618464937e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003330865063057085</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002152060284708168</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0003146439964601071</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6.495253466870519e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.893419908793073e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0006399645409071786</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002328678040967738</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003353466683368755</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.854302584824444e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.136561483090367e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0003690085334665772</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.002925499187527579</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003908400651516011</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1166,4 +1167,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>665.7618226500772</v>
+      </c>
+      <c r="L2" t="n">
+        <v>553.8680807167175</v>
+      </c>
+      <c r="M2" t="n">
+        <v>70793.5672087636</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.004980067818844</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.000632109779071</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>168.9862884015779</v>
+      </c>
+      <c r="L3" t="n">
+        <v>139.2129629309397</v>
+      </c>
+      <c r="M3" t="n">
+        <v>17827.60484991354</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.019920271399725</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.005630221971905</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.870860247252472e-06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.960184382678012e-06</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.735398711624483e-05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.510593476481106e-05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.533821351926326e-05</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.116134045943466e-07</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.330858443737368e-06</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.911544829395652e-06</v>
+      </c>
+      <c r="N5" t="n">
+        <v>8.816936366488134e-06</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6.111379327572627e-06</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.277648137875678e-06</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.915671566793235e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.738573980322768e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.383347910860905e-05</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.696651309030403e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.457342753619084e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.740335787215339e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.833219817946181e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0001784319721954718</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8.266983309300303e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.84821999319007e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.291081211478899e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>7.263434637677486e-05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0003567328616449983</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001581588011359161</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.056665411173887e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.71685296937941e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001263591191629042</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006427341865389303</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0002770334149182972</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.411263847585281e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.365443736716422e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002072355055718267</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001080103523233787</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004566224662484408</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0001984342815989359</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.000216807588289907</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0004804638643950197</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002580219472922798</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.001065419351539192</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0009707284355454646</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.001039717910279494</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.002308171972573587</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.01277836975557997</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.005150274720021671</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.003037685007988621</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.003229920792057779</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.007175584347927515</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.04007608151122834</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01601274416433614</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01548377342090667</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.01637310402963263</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.03638373085342465</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.201741298992963</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.08010316856534344</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>500</v>
+      </c>
+      <c r="B15" t="n">
+        <v>500</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.05101364699212206</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.05381310509724311</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.119430154445692</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6362557902277538</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.25207347140194</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>500</v>
+      </c>
+      <c r="B16" t="n">
+        <v>500</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.3548365886464349</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3731185274916085</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8192773159447639</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.215019770958544</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.271721145014258</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2093,4 +2094,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.411263847585281e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.365443736716422e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002072355055718267</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001080103523233787</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004566224662484408</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.42724338215861e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.382757058287389e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002076017954712379</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001081350392173331</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004573455532124901</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001966567907588645</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002182998963120192</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0004858512100801628</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.002518444047118838</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.001064672517884572</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.000494302288392756</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004574967382495188</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001089574096721313</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.005288145594616679</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.002171636878331381</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.001998045723772656</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0008978428079064211</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005056208725613049</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.006922567656685288</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.002618346221493335</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.00102702225355622</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0008212502051493084</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.00904712566806375</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.01056789879714007</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.003841717570886462</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.07567317838684853</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.03347227769746421</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2593546716679164</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0182505445030345</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.005577947594335745</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.003347742282752807</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.002237757579184933</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01092773022684849</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02369502118423353</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.007446217802241049</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01857140797167433</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.006536910976184223</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.03984277832774872</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.03670244342852896</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.009181126864706853</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2690,4 +2691,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.411263847585281e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.365443736716422e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002072355055718267</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001080103523233787</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004566224662484408</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8.427161735280463e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.382685862122441e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0002076176141537447</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001082216193252291</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004574712035892125</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.419879227394843e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.373488506847377e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002074171005758666</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001081354475671217</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0004570515004581796</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8.412233779131471e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.366452995830066e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000207257602146738</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001080223889116438</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0004566696232419237</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.402409205798821e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.355828462195352e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002070221958682497</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001078944365393588</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0004561475527113217</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.40248851485814e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.355883742687882e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002070233016820101</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001078964170668557</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004561487323724905</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.404921943938602e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.358535477090763e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002070820451360538</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00107923531323705</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004562790263677389</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8.409490655791883e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.363546492079902e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002071933943626905</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001079876448625142</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004565294581726278</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.399807609416053e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.353359991078479e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002069664038199265</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00107859233330557</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004560150651932776</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.391383591122013e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.344902871634449e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.000206777080137797</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001077471889240814</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0004555795198235157</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3342,4 +3343,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.220198767331596e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>8.206183909218945e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001884220671921508</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001079692886295644</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004569272346059696</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.907744121141921e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.012518542022926e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001844188199947954</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001079727158260842</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004569316165134347</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.668861754387632e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.828159337584437e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.000179860600925269</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001079877736628987</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0004568862712033554</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.703369679627145e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.861842417705825e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.000180776710040462</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001079953440542643</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0004568242841990786</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.222191387172947e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8.208766106868872e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001884816601850412</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001080062924302102</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0004566873090908405</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.622282164048253e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.443213622152751e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0001927769533856855</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.00108008255033162</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004566570670519959</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.547112166617075e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.954065592473792e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0002010933693096531</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001080099508321333</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004566292067939793</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.87013101016809e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.117590678561054e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002035800336385337</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001080101837236723</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004566255139965204</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.411263847585281e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.365443736716422e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002072355055718267</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001080103523233787</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004566224662484408</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>500</v>
+      </c>
+      <c r="B11" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.567463968089938e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>9.42935359133615e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0002081550940321763</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001080103823076203</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0004566220869984963</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>500</v>
+      </c>
+      <c r="B12" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.805606319239877e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>9.517449664673412e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.000209395914733287</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.001080103975915104</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0004566217651170453</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>500</v>
+      </c>
+      <c r="B13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.868431539010845e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>9.538497711228206e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0002096833291577007</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.00108010394682187</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0004566217204857111</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>500</v>
+      </c>
+      <c r="B14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.957430512412933e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>9.565267219778936e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0002100396030435061</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001080104016456205</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0004566217058239015</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_5.xlsx
+++ b/Results/rbf_fd_parameter_study_5.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4159,4 +4160,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>500</v>
+      </c>
+      <c r="B2" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>8.407926580777934e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.361824607284995e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0002071552623475662</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001079652082085809</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0004564436142533155</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>500</v>
+      </c>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5.764359110882465e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.91178340525159e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001427470275306276</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001079767479791186</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004564893225663376</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>500</v>
+      </c>
+      <c r="B4" t="n">
+        <v>500</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.668875793130022e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.828178549874422e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001370551566263092</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001079880696889886</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.000456534170755815</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.76547286317841e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.913296309994899e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001427745058829067</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.001079993281612649</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0004565787367263538</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>500</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.411263847585281e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.365443736716422e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002072355055718267</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.001080103523233787</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0004566224662484408</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>500</v>
+      </c>
+      <c r="B7" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.765448164773977e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.913262904312929e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0003049905550328564</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001079988404322381</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004565767505559558</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>500</v>
+      </c>
+      <c r="B8" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.668847978507195e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.828140472911234e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003559376267078346</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001079875114536792</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004565318744939771</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>500</v>
+      </c>
+      <c r="B9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.764334704705386e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7.911750170968964e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0003049319367483311</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001079762740606007</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004564873442283667</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>500</v>
+      </c>
+      <c r="B10" t="n">
+        <v>500</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.407926580777934e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9.361824607284995e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002071552623475663</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001079652082085809</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0004564436142533155</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>